--- a/artfynd/A 18274-2023 artfynd.xlsx
+++ b/artfynd/A 18274-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,6 +1143,726 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114883525</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>614517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6778804</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114884453</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>614492</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6778813</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114883238</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>614492</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6778767</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114884450</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>614736</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6778923</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114883523</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>614551</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6778873</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114884451</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614698</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6778908</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>

--- a/artfynd/A 18274-2023 artfynd.xlsx
+++ b/artfynd/A 18274-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114883238</v>
+        <v>114884001</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,17 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614492</v>
+        <v>614678</v>
       </c>
       <c r="R2" t="n">
-        <v>6778767</v>
+        <v>6778880</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114884451</v>
+        <v>114884533</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614698</v>
+        <v>614646</v>
       </c>
       <c r="R3" t="n">
-        <v>6778908</v>
+        <v>6778808</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -915,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114883525</v>
+        <v>114883628</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +911,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -969,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614518</v>
+        <v>614753</v>
       </c>
       <c r="R4" t="n">
-        <v>6778804</v>
+        <v>6778884</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1035,37 +1015,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114884533</v>
+        <v>114883523</v>
       </c>
       <c r="B5" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1089,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614646</v>
+        <v>614552</v>
       </c>
       <c r="R5" t="n">
-        <v>6778808</v>
+        <v>6778873</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,12 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114883523</v>
+        <v>114883524</v>
       </c>
       <c r="B6" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614552</v>
+        <v>614654</v>
       </c>
       <c r="R6" t="n">
-        <v>6778873</v>
+        <v>6778785</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1275,52 +1245,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114883255</v>
+        <v>114883525</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614713</v>
+        <v>614518</v>
       </c>
       <c r="R7" t="n">
-        <v>6778839</v>
+        <v>6778804</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,12 +1363,7 @@
         <v>114884450</v>
       </c>
       <c r="B8" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,15 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114884453</v>
+        <v>114884451</v>
       </c>
       <c r="B9" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614493</v>
+        <v>614698</v>
       </c>
       <c r="R9" t="n">
-        <v>6778813</v>
+        <v>6778908</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1635,32 +1590,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114883628</v>
+        <v>114884452</v>
       </c>
       <c r="B10" t="n">
-        <v>57591</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1673,14 +1623,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1689,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>614753</v>
+        <v>614509</v>
       </c>
       <c r="R10" t="n">
-        <v>6778884</v>
+        <v>6778745</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,12 +1664,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,32 +1700,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114884001</v>
+        <v>114884453</v>
       </c>
       <c r="B11" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1793,6 +1733,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1804,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614678</v>
+        <v>614493</v>
       </c>
       <c r="R11" t="n">
-        <v>6778880</v>
+        <v>6778813</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1834,12 +1779,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1804,585 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114883508</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>614498</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6778738</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114883255</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>614713</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6778839</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114883238</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>614492</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6778767</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114883339</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>614562</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6778736</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114884244</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>614659</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6778838</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>

--- a/artfynd/A 18274-2023 artfynd.xlsx
+++ b/artfynd/A 18274-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883628</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883523</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883524</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883525</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884451</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884453</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2042,6 +2102,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883255</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883238</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2272,6 +2342,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883339</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2387,8 +2462,30 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884244</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>